--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -493,10 +493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>Validador de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>Validador de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -643,9 +643,321 @@
         <v>Error:</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Convertir a XML</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Convertir a JSON</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Convertir a ICC</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Convirtiendo a XML…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Convirtiendo a JSON…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Convirtiendo a ICC…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Cargar perfil ICC</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Zona de soltado para archivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ID del perfil</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>No se encontraron etiquetas.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Nombre de etiqueta</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Desplazamiento</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Tamaño</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Relleno</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Bytes modificados desde la carga</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(Sin contenido)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Cargando descripción completa…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>No se pudo cargar la descripción completa:</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Sin salida de validación</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -869,95 +869,175 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>sangría</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>ordenar claves</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -821,223 +821,239 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>Sin salida de validación</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>Válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>Advertencia</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>Error</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>Desconocido</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>Ver en contexto</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>Detalle de validación</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>Activado por</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>Campo</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>Valor actual</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>Requerido: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>No válido</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>Cerrar</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>ordenar claves</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -845,215 +845,263 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>Válido</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>Advertencia</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>Error</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>Desconocido</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>Ver en contexto</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>Detalle de validación</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>Activado por</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>Campo</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>Valor actual</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>Requerido: 0</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>Esperado: {value}</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>No válido</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>Cerrar</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>sangría</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>ordenar claves</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,503 +605,591 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>Salida bruta</v>
+        <v>Profile Assessment WG</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>Error:</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>Convertir a XML</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>Convertir a JSON</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>Convertir a ICC</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>Cargar perfil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>ID del perfil</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>Desplazamiento</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>Tamaño</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>Relleno</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>Tipo</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>Array de {type}</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>(Sin contenido)</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>bytes</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>Sin salida de validación</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>El perfil es válido</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>Error de validación crítico</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>Válido</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>Advertencia</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>Error</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>Desconocido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>Ver en contexto</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>Detalle de validación</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>Activado por</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>Campo</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>Valor actual</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>Requerido: 0</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>Esperado: {value}</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>No válido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>Cerrar</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>sangría</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>ordenar claves</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -637,23 +637,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -669,7 +669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -677,7 +677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -685,7 +685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -693,7 +693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -701,7 +701,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -709,7 +709,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -717,479 +717,495 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>Error:</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>Convertir a XML</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>Convertir a JSON</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>ID del perfil</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>Desplazamiento</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>Tamaño</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>Relleno</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>Tipo</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>Array de {type}</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>(Sin contenido)</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>bytes</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>Sin salida de validación</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>El perfil es válido</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>Válido</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>Advertencia</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>Error</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>Desconocido</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>Ver en contexto</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>Detalle de validación</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>Activado por</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>Campo</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>Valor actual</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>Requerido: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>No válido</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>Cerrar</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>ordenar claves</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -512,12 +512,12 @@
         <v>specification using the</v>
       </c>
       <c r="B14" t="str">
-        <v>usando la implementación de referencia</v>
+        <v>usando la implementación de demostración</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
         <v>.</v>
@@ -525,687 +525,919 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>Validando…</v>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>Guardar perfil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>o</v>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>Elegir archivo</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>o</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>Encabezado</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>Etiquetas</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>Validación</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>Salida bruta</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>Error:</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>Convertir a XML</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>Convertir a JSON</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>Convertir a ICC</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>ID del perfil</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>Desplazamiento</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>Tamaño</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>Relleno</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>Tipo</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>Array de {type}</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>(Sin contenido)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>bytes</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>Cargando descripción completa…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>Sin salida de validación</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>El perfil es válido</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>Error de validación crítico</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>Válido</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>Advertencia</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>Error</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>Desconocido</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>Ver en contexto</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>Detalle de validación</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Activado por</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>Campo</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>Valor actual</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>Requerido: 0</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>Esperado: {value}</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>No válido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>Cerrar</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>Cargando editor XML…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>sangría</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>ordenar claves</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Estado de validación desconocido</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Crítico — mostrado solo para inspección</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -861,583 +861,575 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>Error:</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>Convertir a XML</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>ID del perfil</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>Desplazamiento</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>Tamaño</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>Relleno</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>Tipo</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>Array de {type}</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>(Sin contenido)</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>bytes</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>Sin salida de validación</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>El perfil es válido</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>Error de validación crítico</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>Válido</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>Advertencia</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>Error</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>Desconocido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>Aprobado</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>Fallido</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>Ver en contexto</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>Detalle de validación</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>Activado por</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>Campo</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>Valor actual</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>Requerido: 0</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>Esperado: {value}</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>No válido</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>Cerrar</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>sangría</v>
+        <v>ordenar claves</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>ordenar claves</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -477,959 +477,983 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>Ayuda</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>Contacto</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>Sube un perfil ICC para validarlo según la especificación</v>
+        <v>Ayuda</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>usando la implementación de demostración</v>
+        <v>Contacto</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>.</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v>Basado en la implementación de demostración de</v>
+        <v>Sube un perfil ICC para validarlo según la especificación</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>usando la implementación de demostración</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>Validando…</v>
+        <v>.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>o</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>Elegir archivo</v>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>Encabezado</v>
+        <v>o</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>Etiquetas</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>Validación</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>Gráfico</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>Salida bruta</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>Curvas</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>Curvas de entrada</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>Curvas de salida</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>Imagen CLUT</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>Imagen de gama</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>Cromaticidad</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>Tabla de la curva</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>Tablas</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>Datos</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>Evaluar</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>Cargando…</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>Entrada</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>Salida</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>Coma flotante</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>Normalizado</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>Legible</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>Cargando…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>Seguridad</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>Conformidad</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>Calidad</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>INFORME</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>FALLIDO</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>comprobaciones</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>Error:</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>Convertir a XML</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>Convertir a JSON</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>Convertir a ICC</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>ID del perfil</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>Desplazamiento</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>Tamaño</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>Relleno</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>Tipo</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>Array de {type}</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>(Sin contenido)</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>bytes</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>Sin salida de validación</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>El perfil es válido</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>Válido</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>Advertencia</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>Error</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>Desconocido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>Aprobado</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>Fallido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>Ver en contexto</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>Detalle de validación</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>Activado por</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>Campo</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>Valor actual</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>Requerido: 0</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>Esperado: {value}</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>No válido</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>Cerrar</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>Cargando editor XML…</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>sangría</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>ordenar claves</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -885,575 +885,583 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>Seguridad</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>Conformidad</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>Calidad</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>INFORME</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>Error:</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -645,823 +645,1215 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>Gráfico</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>Salida bruta</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>Curvas</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>Curvas de entrada</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>Curvas de salida</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>Imagen CLUT</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>Imagen de gama</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>Cromaticidad</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Los canales con muchas inversiones muestran solo las {shown} mayores por ΔL*.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Mostrar más ({n})</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>Tabla de la curva</v>
+        <v>Todos</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>Tablas</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>Datos</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>Evaluar</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>Cargando…</v>
+        <v>Inversión de tono L*</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>Entrada</v>
+        <v>Añadir tinta nunca debería aclarar un color. Cada canal se recorre manteniendo fijos los demás; se marca todo paso en el que L* aumenta. Algoritmo originalmente de Harold Boll.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>Salida</v>
+        <v>Este perfil no tiene una CLUT dispositivo→PCS, así que el análisis de inversión L* no se aplica (por ejemplo, un perfil de pantalla de matriz/TRC).</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>Coma flotante</v>
+        <v>Tabla LUT</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Umbral ΔL* (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>Normalizado</v>
+        <v>{n} inversiones por encima de ε = {eps}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>Legible</v>
+        <v>Sin inversiones L* por encima de ε = {eps}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Tinta (bajo → alto)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>Cargando…</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>Seguridad</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>Conformidad</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>Calidad</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>INFORME</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>FALLIDO</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>comprobaciones</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>Error:</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>Convertir a XML</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>Convertir a JSON</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>Convertir a ICC</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>ID del perfil</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>Desplazamiento</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>Tamaño</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>Relleno</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>Tipo</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>Array de {type}</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>(Sin contenido)</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>bytes</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>Sin salida de validación</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>El perfil es válido</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>Error de validación crítico</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>Válido</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>Advertencia</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>Error</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>Desconocido</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>Aprobado</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>Fallido</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>Ver en contexto</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>Detalle de validación</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>Activado por</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>Campo</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>Valor actual</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>Requerido: 0</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>Esperado: {value}</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>No válido</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>Cerrar</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>sangría</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>ordenar claves</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>No se encontraron etiquetas.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Nombre de etiqueta</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Desplazamiento</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Tamaño</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Relleno</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Bytes modificados desde la carga</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(Sin contenido)</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Cargando descripción completa…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>No se pudo cargar la descripción completa:</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Sin salida de validación</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>El perfil es válido</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>El perfil tiene advertencias</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>El perfil no es conforme</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Error de validación crítico</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Estado de validación desconocido</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Crítico — mostrado solo para inspección</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,1343 +517,1415 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Guía del usuario</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>Sube un perfil ICC para validarlo según la especificación</v>
+        <v>Buscar en la guía</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>usando la implementación de demostración</v>
+        <v>Buscar en la guía del usuario</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>.</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v>Basado en la implementación de demostración de</v>
+        <v>Resultado siguiente</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Cerrar la guía</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>Validando…</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>No se pudo cargar la guía del usuario.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v>Ninguno</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>o</v>
+        <v>Sube un perfil ICC para validarlo según la especificación</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>Elegir archivo</v>
+        <v>usando la implementación de demostración</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>Encabezado</v>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>Etiquetas</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>Validación</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>Análisis</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>o</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>Propósito de representación</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% tinta</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>Perceptual</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>Saturación</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>Los canales con muchas inversiones muestran solo las {shown} mayores por ΔL*.</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>Mostrar más ({n})</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>Todos</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>Analizando…</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>Análisis</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>Inversión de tono L*</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>Añadir tinta nunca debería aclarar un color. Cada canal se recorre manteniendo fijos los demás; se marca todo paso en el que L* aumenta. Algoritmo originalmente de Harold Boll.</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>Este perfil no tiene una CLUT dispositivo→PCS, así que el análisis de inversión L* no se aplica (por ejemplo, un perfil de pantalla de matriz/TRC).</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>Tabla LUT</v>
+        <v>Los canales con muchas inversiones muestran solo las {shown} mayores por ΔL*.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>Umbral ΔL* (ε)</v>
+        <v>Mostrar más ({n})</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>{n} inversiones por encima de ε = {eps}</v>
+        <v>Todos</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>Sin inversiones L* por encima de ε = {eps}</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>Canal</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>Tinta (bajo → alto)</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>Gráfico</v>
+        <v>Inversión de tono L*</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>Salida bruta</v>
+        <v>Añadir tinta nunca debería aclarar un color. Cada canal se recorre manteniendo fijos los demás; se marca todo paso en el que L* aumenta. Algoritmo originalmente de Harold Boll.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>Este perfil no tiene una CLUT dispositivo→PCS, así que el análisis de inversión L* no se aplica (por ejemplo, un perfil de pantalla de matriz/TRC).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>Tabla LUT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>Curvas</v>
+        <v>Umbral ΔL* (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>Curvas de entrada</v>
+        <v>{n} inversiones por encima de ε = {eps}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>Curvas de salida</v>
+        <v>Sin inversiones L* por encima de ε = {eps}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>Imagen CLUT</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>Imagen de gama</v>
+        <v>Tinta (bajo → alto)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>Cromaticidad</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>Tabla de la curva</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tablas</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Datos</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>Evaluar</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>Cargando…</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>Entrada</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>Salida</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Coma flotante</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>Normalizado</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>Legible</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>Cargando…</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>Seguridad</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>Conformidad</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>Calidad</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>INFORME</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>FALLIDO</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>comprobaciones</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>Suscribirse</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>Cerrar</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>Correo electrónico</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>(opcional)</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>Cancelar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>Suscribirse</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>Cerrar</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>Aviso de privacidad</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>Error:</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>Convertir a XML</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>Convertir a JSON</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>Convertir a ICC</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>ID del perfil</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>Desplazamiento</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>Tamaño</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>Relleno</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>Tipo</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>Array de {type}</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>(Sin contenido)</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>bytes</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>Sin salida de validación</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>El perfil es válido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>El perfil no es conforme</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>Error de validación crítico</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>Válido</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>Advertencia</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>Error</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>Desconocido</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>Aprobado</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>Fallido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>Ver en contexto</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>Detalle de validación</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>Activado por</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>Campo</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>Valor actual</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>Requerido: 0</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>Esperado: {value}</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>No válido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>Cerrar</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>sangría</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>ordenar claves</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -797,330 +797,330 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>Los canales con muchas inversiones muestran solo las {shown} mayores por ΔL*.</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>Mostrar más ({n})</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>Todos</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>Analizando…</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>Análisis</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>Inversión de tono L*</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>Añadir tinta nunca debería aclarar un color. Cada canal se recorre manteniendo fijos los demás; se marca todo paso en el que L* aumenta. Algoritmo originalmente de Harold Boll.</v>
+        <v>media</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>Este perfil no tiene una CLUT dispositivo→PCS, así que el análisis de inversión L* no se aplica (por ejemplo, un perfil de pantalla de matriz/TRC).</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>Tabla LUT</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>Umbral ΔL* (ε)</v>
+        <v>Los canales con muchas inversiones muestran solo las {shown} mayores por ΔL*.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>{n} inversiones por encima de ε = {eps}</v>
+        <v>Mostrar más ({n})</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>Sin inversiones L* por encima de ε = {eps}</v>
+        <v>Todos</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>Canal</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>Tinta (bajo → alto)</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>Gráfico</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>Salida bruta</v>
+        <v>Inversión de tono L*</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>Añadir tinta nunca debería aclarar un color. Cada canal se recorre manteniendo fijos los demás; se marca todo paso en el que L* aumenta. Algoritmo originalmente de Harold Boll.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>Este perfil no tiene una CLUT dispositivo→PCS, así que el análisis de inversión L* no se aplica (por ejemplo, un perfil de pantalla de matriz/TRC).</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>Curvas</v>
+        <v>Tabla LUT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>Curvas de entrada</v>
+        <v>Umbral ΔL* (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>Curvas de salida</v>
+        <v>{n} inversiones por encima de ε = {eps}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>Imagen CLUT</v>
+        <v>Sin inversiones L* por encima de ε = {eps}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>Imagen de gama</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>Cromaticidad</v>
+        <v>Tinta (bajo → alto)</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>Tabla de la curva</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>Tablas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>Datos</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>Evaluar</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>Cargando…</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>Entrada</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>Salida</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>Coma flotante</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>Normalizado</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>Legible</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="91">
@@ -1133,799 +1133,879 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>Seguridad</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>Conformidad</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>Calidad</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>INFORME</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>FALLIDO</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>comprobaciones</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>Suscribirse</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>Cerrar</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>Correo electrónico</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>(opcional)</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>Cancelar</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>Suscribirse</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>Cerrar</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>Aviso de privacidad</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>Error:</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>Convertir a XML</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>Convertir a JSON</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>Convertir a ICC</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>ID del perfil</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>Desplazamiento</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>Tamaño</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>Relleno</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>Tipo</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>Array de {type}</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>(Sin contenido)</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>bytes</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>Sin salida de validación</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>El perfil es válido</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>Error de validación crítico</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>Válido</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>Advertencia</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>Error</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>Desconocido</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>Aprobado</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>Fallido</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>Ver en contexto</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>Detalle de validación</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>Activado por</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>Campo</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>Valor actual</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>Requerido: 0</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>Esperado: {value}</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>No válido</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>Cerrar</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>sangría</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>ordenar claves</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -877,474 +877,474 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>Los canales con muchas inversiones muestran solo las {shown} mayores por ΔL*.</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>Mostrar más ({n})</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>Todos</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>Analizando…</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>Análisis</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>Inversión de tono L*</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>Añadir tinta nunca debería aclarar un color. Cada canal se recorre manteniendo fijos los demás; se marca todo paso en el que L* aumenta. Algoritmo originalmente de Harold Boll.</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Este perfil no tiene una CLUT dispositivo→PCS, así que el análisis de inversión L* no se aplica (por ejemplo, un perfil de pantalla de matriz/TRC).</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tabla LUT</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>Umbral ΔL* (ε)</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>{n} inversiones por encima de ε = {eps}</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>Sin inversiones L* por encima de ε = {eps}</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>Canal</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>Tinta (bajo → alto)</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>Gráfico</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>Salida bruta</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Curvas</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>Curvas de entrada</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>Curvas de salida</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>Imagen CLUT</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>Imagen de gama</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>Cromaticidad</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>Tabla de la curva</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>Tablas</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>Datos</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>Evaluar</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>Cargando…</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>Entrada</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>Salida</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>Coma flotante</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>Normalizado</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>Legible</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>Cargando…</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Seguridad</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>Conformidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>Calidad</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>INFORME</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>FALLIDO</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>comprobaciones</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="119">
@@ -1357,18 +1357,18 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="122">
@@ -1381,631 +1381,535 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>Correo electrónico</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>(opcional)</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>Cancelar</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>Suscribirse</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>Cerrar</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>Convertir a XML</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>Convertir a JSON</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>Convertir a ICC</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>ID del perfil</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>Desplazamiento</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>Tamaño</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>Relleno</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>Tipo</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>Array de {type}</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>(Sin contenido)</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>bytes</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>Sin salida de validación</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>El perfil es válido</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>Error de validación crítico</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>Válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>Advertencia</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>Error</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>Desconocido</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>Aprobado</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Fallido</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>Ver en contexto</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Detalle de validación</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>Activado por</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>Campo</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>Valor actual</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Requerido: 0</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>Esperado: {value}</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>No válido</v>
+        <v>ordenar claves</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>Cerrar</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>Cargando editor XML…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>Cargando editor JSON…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● ediciones XML sin guardar</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● ediciones JSON sin guardar</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>sangría</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>ordenar claves</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -853,1063 +853,1071 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>media</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>Analizando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>Análisis</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>Gráfico</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>Salida bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Curvas de salida</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Imagen CLUT</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>Imagen de gama</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>Cromaticidad</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>Tabla de la curva</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>Tablas</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>Datos</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>Evaluar</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>Cargando…</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>Entrada</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>Salida</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>Coma flotante</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>Normalizado</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>Legible</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>Cargando…</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>Seguridad</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>Conformidad</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>Calidad</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>INFORME</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>Correo electrónico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>(opcional)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>Cancelar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>Suscribirse</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>Cerrar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Error:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,1511 +413,1887 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>Ajustes</v>
+        <v>Ida y vuelta (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>Visualización</v>
+        <v>Ida y vuelta sobre el cubo del dispositivo del perfil, igual que la herramienta de referencia iccRoundTrip. La ida y vuelta 1 es el error dispositivo→PCS→dispositivo (ΔE*ab); la ida y vuelta 2 mide la estabilidad del ciclo PCS. El histograma PRMG indica la interoperabilidad respecto al Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>Fondo</v>
+        <v>Usar etiquetas MPE (color)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>Idioma</v>
+        <v>Este perfil no admite ida y vuelta: carece de las transformaciones dispositivo↔PCS necesarias (p. ej. un perfil unidireccional o abstracto).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>Sistema</v>
+        <v>Ida y vuelta omitida: el espacio de color del dispositivo es demasiado amplio para evaluar (demasiadas muestras).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>Claro</v>
+        <v>Métrica</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>Oscuro</v>
+        <v>Ida y vuelta 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>Predeterminado del sistema</v>
+        <v>Ida y vuelta 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>Formato numérico</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>Hexadecimal</v>
+        <v>estabilidad del ciclo PCS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>Decimal</v>
+        <v>ΔE mín</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Ayuda</v>
+        <v>ΔE medio</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Contacto</v>
+        <v>ΔE máx</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>Guía del usuario</v>
+        <v>Peor L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>Buscar en la guía</v>
+        <v>Gama especificada</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Buscar en la guía del usuario</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>Resultado anterior</v>
+        <v>No especificada</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>Resultado siguiente</v>
+        <v>No evaluada</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>Cerrar la guía</v>
+        <v>Interoperabilidad PRMG</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>Cargando…</v>
+        <v>ΔE de ida y vuelta</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>No se pudo cargar la guía del usuario.</v>
+        <v>Recuento</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>Ninguno</v>
+        <v>Proporción</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>Sube un perfil ICC para validarlo según la especificación</v>
+        <v>PRMG no evaluado</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>usando la implementación de demostración</v>
+        <v>Ajustes</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>.</v>
+        <v>Visualización</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v>Basado en la implementación de demostración de</v>
+        <v>Fondo</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>Validando…</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Claro</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v>Oscuro</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Predeterminado del sistema</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>o</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>Elegir archivo</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>Encabezado</v>
+        <v>Ayuda</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>Etiquetas</v>
+        <v>Contacto</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>Validación</v>
+        <v>Guía del usuario</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>Análisis</v>
+        <v>Buscar en la guía</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>Buscar en la guía del usuario</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>Resultado siguiente</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>Cerrar la guía</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>Propósito de representación</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% tinta</v>
+        <v>No se pudo cargar la guía del usuario.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>Perceptual</v>
+        <v>Ninguno</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>Saturación</v>
+        <v>Sube un perfil ICC para validarlo según la especificación</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>usando la implementación de demostración</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>Propósito de representación</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>ΔE de ciclo</v>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>media</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>máx.</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>Analizando…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>Análisis</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>Gráfico</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>Salida bruta</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>Curvas</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>Curvas de entrada</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>Curvas de salida</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>Imagen CLUT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>Imagen de gama</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>Cromaticidad</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>Gráfico de dispersión</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>Tabla de la curva</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>Tablas</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>Datos</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>Evaluar</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>Cargando…</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>Entrada</v>
+        <v>o</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>Salida</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>Coma flotante</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>Normalizado</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>Legible</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>Cargando…</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>Seguridad</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>Conformidad</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>Calidad</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>INFORME</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>FALLIDO</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>comprobaciones</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>media</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>Suscribirse</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>Cerrar</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>Correo electrónico</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>(opcional)</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>Cancelar</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>Suscribirse</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>Cerrar</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>Error:</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>Convertir a XML</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>Convertir a JSON</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>Convertir a ICC</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>ID del perfil</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>Desplazamiento</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>Tamaño</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>Relleno</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>Tipo</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>Array de {type}</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>(Sin contenido)</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>bytes</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>Sin salida de validación</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>El perfil es válido</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>Error de validación crítico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>Válido</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>Advertencia</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>Error</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>Desconocido</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>Aprobado</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>Fallido</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>Ver en contexto</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>Detalle de validación</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>Activado por</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>Campo</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>Valor actual</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>Requerido: 0</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>Esperado: {value}</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>No válido</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>Cerrar</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>sangría</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>ordenar claves</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Desplazamiento</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Tamaño</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Relleno</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Bytes modificados desde la carga</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(Sin contenido)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Cargando descripción completa…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>No se pudo cargar la descripción completa:</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Sin salida de validación</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>El perfil es válido</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>El perfil tiene advertencias</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>El perfil no es conforme</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Error de validación crítico</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Estado de validación desconocido</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Crítico — mostrado solo para inspección</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,1695 +605,2365 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>Ajustes</v>
+        <v>Métricas de todo el perfil para un propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y una métrica de precisión de ida y vuelta. Elige el propósito de representación y el tipo de ida y vuelta — la tabla y el histograma se actualizan en consecuencia.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>Visualización</v>
+        <v>Tipo de ida y vuelta</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Fondo</v>
+        <v>No afecta a este tipo de ida y vuelta</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>Idioma</v>
+        <v>Este tipo de ida y vuelta no está disponible para este perfil.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>Sistema</v>
+        <v>Distribución del ΔE de ida y vuelta</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>Claro</v>
+        <v>Ninguna muestra de ida y vuelta cayó dentro de la región evaluada.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>Oscuro</v>
+        <v>Desv. típica</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>Predeterminado del sistema</v>
+        <v>Frecuencia relativa</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Formato numérico</v>
+        <v>Frecuencia acumulada</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>Hexadecimal</v>
+        <v>Escala horizontal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>Decimal</v>
+        <v>ΔE entero</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>Ayuda</v>
+        <v>Escala automática</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>Contacto</v>
+        <v>Clases</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>Guía del usuario</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>Buscar en la guía</v>
+        <v>La tabla de consulta de color (CLUT) de una transformación dispositivo↔PCS, dispuesta en mosaico en una imagen. Elige qué tabla de propósito de representación mostrar.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>Buscar en la guía del usuario</v>
+        <v>Este perfil no tiene tablas dispositivo↔PCS basadas en CLUT para visualizar.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>Resultado anterior</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>Resultado siguiente</v>
+        <v>El mapa dentro/fuera de gama de la etiqueta gamut: neutro donde un color PCS es reproducible, rojo donde queda fuera de la gama del dispositivo.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>Cerrar la guía</v>
+        <v>Este perfil no tiene etiqueta gamut para visualizar.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>Cargando…</v>
+        <v>Escala vertical</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>No se pudo cargar la guía del usuario.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>Ninguno</v>
+        <v>Incremento tonal</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Incremento tonal (salida − entrada)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>Sube un perfil ICC para validarlo según la especificación</v>
+        <v>Mostrar volcado completo</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>usando la implementación de demostración</v>
+        <v>Salida truncada por rendimiento.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>.</v>
+        <v>Resumen dentro de gama (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v>Basado en la implementación de demostración de</v>
+        <v>Inversión + gama (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Reproducibilidad (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>Validando…</v>
+        <v>Interoperabilidad PRMG</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Resumen de iccviz: una cuadrícula de valores de dispositivo se lleva al PCS, de vuelta al dispositivo y de nuevo al PCS; se mide el ΔE*ab entre las dos pasadas de PCS. Una comprobación rápida de estabilidad dentro de la gama.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v>iccRoundTrip Ida y vuelta 1: ΔE*ab entre el PCS de cada color de dispositivo y su PCS tras una ida y vuelta Lab → dispositivo → Lab. Refleja la precisión de inversión y el mapeo de gama.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip Ida y vuelta 2: ΔE*ab entre la primera y la segunda ida y vuelta — cómo de estable es una ida y vuelta de PCS repetida (reproducibilidad, independiente del recorte de gama de la primera pasada).</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG: los colores PCS dentro del Perceptual Reference Medium Gamut realizan una única ida y vuelta (Lab → dispositivo → Lab); la distribución del ΔE*ab indica la interoperabilidad entre perfiles.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Ajustes</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Visualización</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Fondo</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Claro</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Oscuro</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Predeterminado del sistema</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Ayuda</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Contacto</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Guía del usuario</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Buscar en la guía</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Buscar en la guía del usuario</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Resultado siguiente</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Cerrar la guía</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>No se pudo cargar la guía del usuario.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Ninguno</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>o</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>Elegir archivo</v>
+        <v>Sube un perfil ICC para validarlo según la especificación</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>usando la implementación de demostración</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>Encabezado</v>
+        <v>.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>Etiquetas</v>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>Validación</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>Análisis</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>Perfiles</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>Mostrar el conjunto de perfiles</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>Propósito de representación</v>
+        <v>Contraer</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% tinta</v>
+        <v>Cargar perfiles</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>Perceptual</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Suelta perfiles ICC aquí</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>Saturación</v>
+        <v>o una imagen (TIFF/PNG/JPEG) para extraer su perfil incrustado — los archivos permanecen en tu dispositivo.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Nuevo desde .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>Ordenar por nombre</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>Nuevo perfil desde .cube</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>Propósito de representación</v>
+        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Elegir archivo .cube</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>ΔE de ciclo</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>o suéltalo aquí, o pega debajo</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>media</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>máx.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>Analizando…</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>Análisis</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>Gráfico</v>
+        <v>Enlazar</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>Salida bruta</v>
+        <v>Arrastra perfiles del conjunto a esta pestaña</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>Ningún perfil seleccionado</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>Curvas</v>
+        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>Curvas de entrada</v>
+        <v>Aún no hay nada que comparar</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>Curvas de salida</v>
+        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>Imagen CLUT</v>
+        <v>Comparación de gama</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>Imagen de gama</v>
+        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>Cromaticidad</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Envoltura</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Malla</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Tabla de la curva</v>
+        <v>Opacidad</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Tablas</v>
+        <v>Color</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Datos</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Evaluar</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Cargando…</v>
+        <v>Por tono</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Entrada</v>
+        <v>Rotación</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Salida</v>
+        <v>Plataforma giratoria</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Coma flotante</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Velocidad de arrastre</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Normalizado</v>
+        <v>Alabeo</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Legible</v>
+        <v>Velocidad de alabeo</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Construyendo la gama…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>sin gama</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Cargando…</v>
+        <v>Envoltura de gama 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Corte de gama 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Enlace</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Seguridad</v>
+        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Conformidad</v>
+        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>Calidad</v>
+        <v>Creador de pantalla V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>INFORME</v>
+        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>FALLIDO</v>
+        <v>Pantalla RGB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>comprobaciones</v>
+        <v>suelta un perfil de pantalla</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>suelta un perfil de observador</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Crear perfil de pantalla V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Suscribirse</v>
+        <v>Nombre del perfil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Crear</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Cerrar</v>
+        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>Correo electrónico</v>
+        <v>{n} archivo(s) no cargados</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Aceptar</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>(opcional)</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>o</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>Cancelar</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>Suscribirse</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>Cerrar</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>Convertir a XML</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>Convertir a JSON</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>Convertir a ICC</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>ID del perfil</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>media</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>Desplazamiento</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>Tamaño</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>Relleno</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>Tipo</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>Array de {type}</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>(Sin contenido)</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>Sin salida de validación</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>El perfil es válido</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>Error de validación crítico</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>Válido</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>Advertencia</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>Error</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>Desconocido</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>Aprobado</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>Fallido</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>Ver en contexto</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>Detalle de validación</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>Activado por</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>Campo</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>Valor actual</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>Requerido: 0</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>Esperado: {value}</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>No válido</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>Cerrar</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>sangría</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>ordenar claves</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Herramienta de perfiles ICC</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Con tecnología de {lib}</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Suscribirse</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Recibir notificaciones sobre nuevas versiones</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Correo electrónico</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>usted@ejemplo.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>¿Para qué usará profiletool?</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(opcional)</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Cancelar</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Suscribirse</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Gracias — le contactaremos.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Aviso de privacidad</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Introduzca una dirección de correo electrónico válida.</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Revise el formulario e inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Error de red. Inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Error:</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Convertir a XML</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Convertir a JSON</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Convertir a ICC</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Convirtiendo a XML…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Convirtiendo a JSON…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Convirtiendo a ICC…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Cargar perfil ICC</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Zona de soltado para archivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>ID del perfil</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>No se encontraron etiquetas.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Nombre de etiqueta</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Desplazamiento</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Tamaño</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Relleno</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Bytes modificados desde la carga</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>(Sin contenido)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Cargando descripción completa…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>No se pudo cargar la descripción completa:</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Sin salida de validación</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>El perfil es válido</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>El perfil tiene advertencias</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>El perfil no es conforme</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Error de validación crítico</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Estado de validación desconocido</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Crítico — mostrado solo para inspección</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>Enlazar</v>
@@ -1299,1671 +1299,2423 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>Arrastra perfiles del conjunto a esta pestaña</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>Quitar</v>
+        <v>Arrastra perfiles del conjunto a esta pestaña</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>Ningún perfil seleccionado</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
+        <v>Ningún perfil seleccionado</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>Aún no hay nada que comparar</v>
+        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
+        <v>Aún no hay nada que comparar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>Comparación de gama</v>
+        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
+        <v>Comparación de gama</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>Propósito de representación</v>
+        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>Envoltura</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>Malla</v>
+        <v>Envoltura</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacidad</v>
+        <v>Malla</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>Color</v>
+        <v>Números de eje</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>Sólido</v>
+        <v>Opacidad</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>Por valor</v>
+        <v>Color</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>Por tono</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotación</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>Plataforma giratoria</v>
+        <v>Por tono</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>Órbita</v>
+        <v>Rotación</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>Velocidad de arrastre</v>
+        <v>Plataforma giratoria</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>Alabeo</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocidad de alabeo</v>
+        <v>Velocidad de arrastre</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>Construyendo la gama…</v>
+        <v>Alabeo</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>sin gama</v>
+        <v>Velocidad de alabeo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Construyendo la gama…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>Envoltura de gama 3D</v>
+        <v>sin gama</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>Corte de gama 2D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>Plano</v>
+        <v>Envoltura de gama 3D</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Corte de gama 2D</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>Enlace</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
+        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
+        <v>Enlace</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>Creador de pantalla V4</v>
+        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
+        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>Pantalla RGB V5</v>
+        <v>Creador de pantalla V4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>suelta un perfil de pantalla</v>
+        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Pantalla RGB V5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>suelta un perfil de observador</v>
+        <v>suelta un perfil de pantalla</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Crear perfil de pantalla V4</v>
+        <v>suelta un perfil de observador</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>Nombre del perfil</v>
+        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Crear</v>
+        <v>Crear perfil de pantalla V4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>Creando…</v>
+        <v>Nombre del perfil</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
+        <v>Crear</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>Cancelar</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n} archivo(s) no cargados</v>
+        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
+        <v>Flujo de enlace</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>Aceptar</v>
+        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Hecho</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>o</v>
+        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>Elegir archivo</v>
+        <v>Comprobando imagen…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>Encabezado</v>
+        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>Etiquetas</v>
+        <v>Transformar imagen</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>Validación</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>Análisis</v>
+        <v>Suelta perfiles para iniciar la cadena</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>eliminado</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>Mover después</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>Subir</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>Propósito de representación</v>
+        <v>Bajar</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% tinta</v>
+        <v>Intención de renderizado (todas)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>Perceptual</v>
+        <v>Intención de renderizado para esta transformación</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>Saturación</v>
+        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>Cadena</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>No se pudo analizar la cadena.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>Comprobando cadena…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>Propósito de representación</v>
+        <v>La cadena no conecta ({detail}).</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>ΔE de ciclo</v>
+        <v>Corrige la cadena antes de procesar imágenes</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>media</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>Nombre del DeviceLink</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>máx.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>Analizando…</v>
+        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>Análisis</v>
+        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Crea una cadena para procesar imágenes</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>Gráfico</v>
+        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>Salida bruta</v>
+        <v>Imagen transformada guardada.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>Curvas</v>
+        <v>Archivo de datos demasiado grande.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>Curvas de entrada</v>
+        <v>Transformar datos</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>Curvas de salida</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>Imagen CLUT</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>Imagen de gama</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>Cromaticidad</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Condición</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>Tabla de la curva</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>Tablas</v>
+        <v>media</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>Datos</v>
+        <v>parches</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>Evaluar</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>Cargando…</v>
+        <v>Resultado de la transformación</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>Entrada</v>
+        <v>{src} → {dst} · {n} parches</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>Salida</v>
+        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>Coma flotante</v>
+        <v>Guardar como</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Guardar</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>Normalizado</v>
+        <v>Invertir transformación</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>Legible</v>
+        <v>Invirtiendo…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Invertir</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>primera etapa</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>Cargando…</v>
+        <v>Datos en {in} → buscar {out}</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Coste ΔE</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Esta imagen tiene un perfil ICC incrustado.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Extraer y añadir a la cadena</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Extrayendo…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Descartar</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>Seguridad</v>
+        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>Conformidad</v>
+        <v>Opciones de salida de imagen</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>Calidad</v>
+        <v>Codificación</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>INFORME</v>
+        <v>Igual que el origen</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>FALLIDO</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>comprobaciones</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Flotante (32 bits)</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Compresión</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Ninguna</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>Suscribirse</v>
+        <v>Compuesto</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Interpolación CMM</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>Cerrar</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Lineal</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>Correo electrónico</v>
+        <v>Incrustar ICC</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Ensamblar TIFF espectral</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>(opcional)</v>
+        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>can</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>Cancelar</v>
+        <v>Ensamblar y guardar</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>Suscribirse</v>
+        <v>Ensamblando…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Se ensamblaron {n} canales.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>Cerrar</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>Aviso de privacidad</v>
+        <v>{n} archivo(s) no cargados</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Aceptar</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>o</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>Error:</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>Convertir a XML</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>Convertir a JSON</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>Convertir a ICC</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>ID del perfil</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>Desplazamiento</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>Tamaño</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>Relleno</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>Tipo</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>Array de {type}</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>(Sin contenido)</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>bytes</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>media</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>Sin salida de validación</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>El perfil es válido</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>Error de validación crítico</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>Válido</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>Advertencia</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>Error</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>Desconocido</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>Aprobado</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>Fallido</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>Ver en contexto</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>Detalle de validación</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>Activado por</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>Campo</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>Valor actual</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>Requerido: 0</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>Esperado: {value}</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>No válido</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>Cerrar</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>sangría</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>ordenar claves</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Cargando el informe de Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Informe de Profile Assessment WG</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Seguridad</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Conformidad</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Calidad</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>INFORME</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>FALLIDO</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>comprobaciones</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Herramienta de perfiles ICC</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Con tecnología de {lib}</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Suscribirse</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Recibir notificaciones sobre nuevas versiones</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Correo electrónico</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>usted@ejemplo.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>¿Para qué usará profiletool?</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>(opcional)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Cancelar</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Suscribirse</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Gracias — le contactaremos.</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Aviso de privacidad</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Introduzca una dirección de correo electrónico válida.</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Revise el formulario e inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Error de red. Inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Error:</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Convertir a XML</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Convertir a JSON</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Convertir a ICC</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Convirtiendo a XML…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Convirtiendo a JSON…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Convirtiendo a ICC…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Cargar perfil ICC</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Zona de soltado para archivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>ID del perfil</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>No se encontraron etiquetas.</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Nombre de etiqueta</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Desplazamiento</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Tamaño</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Relleno</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Bytes modificados desde la carga</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>(Sin contenido)</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Cargando descripción completa…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>No se pudo cargar la descripción completa:</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Sin salida de validación</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>El perfil es válido</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>El perfil tiene advertencias</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>El perfil no es conforme</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Error de validación crítico</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Estado de validación desconocido</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Crítico — mostrado solo para inspección</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1053,2669 +1053,2645 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>Sube un perfil ICC para validarlo según la especificación</v>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>usando la implementación de demostración</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>.</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v>Basado en la implementación de demostración de</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>Validando…</v>
+        <v>Perfiles</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Mostrar el conjunto de perfiles</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v>Contraer</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Perfiles</v>
+        <v>Cargar perfiles</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>Mostrar el conjunto de perfiles</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>Contraer</v>
+        <v>Suelta perfiles ICC aquí</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>Cargar perfiles</v>
+        <v>o una imagen (TIFF/PNG/JPEG) para extraer su perfil incrustado — los archivos permanecen en tu dispositivo.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>Quitar</v>
+        <v>Nuevo desde .cube</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>Suelta perfiles ICC aquí</v>
+        <v>Ordenar por nombre</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>o una imagen (TIFF/PNG/JPEG) para extraer su perfil incrustado — los archivos permanecen en tu dispositivo.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Nuevo desde .cube</v>
+        <v>Nuevo perfil desde .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>Ordenar por nombre</v>
+        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>Elegir archivo .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>Nuevo perfil desde .cube</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Elegir archivo .cube</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
         <v>o suéltalo aquí, o pega debajo</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Cancelar</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Crear DeviceLink</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Creando…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>Cancelar</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>Creando…</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Enlazar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>Perfil</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>Comparar</v>
+        <v>Arrastra perfiles del conjunto a esta pestaña</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>Enlazar</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>Espectral</v>
+        <v>Ningún perfil seleccionado</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>Arrastra perfiles del conjunto a esta pestaña</v>
+        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>Quitar</v>
+        <v>Aún no hay nada que comparar</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>Ningún perfil seleccionado</v>
+        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
+        <v>Comparación de gama</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>Aún no hay nada que comparar</v>
+        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>Comparación de gama</v>
+        <v>Envoltura</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
+        <v>Malla</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>Propósito de representación</v>
+        <v>Números de eje</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>Envoltura</v>
+        <v>Opacidad</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>Malla</v>
+        <v>Color</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>Números de eje</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>Opacidad</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>Color</v>
+        <v>Por tono</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>Sólido</v>
+        <v>Rotación</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>Por valor</v>
+        <v>Plataforma giratoria</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>Por tono</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>Rotación</v>
+        <v>Velocidad de arrastre</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>Plataforma giratoria</v>
+        <v>Alabeo</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>Órbita</v>
+        <v>Velocidad de alabeo</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocidad de arrastre</v>
+        <v>Construyendo la gama…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>Alabeo</v>
+        <v>sin gama</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocidad de alabeo</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>Construyendo la gama…</v>
+        <v>Envoltura de gama 3D</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>sin gama</v>
+        <v>Corte de gama 2D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>Envoltura de gama 3D</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>Corte de gama 2D</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>Plano</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>Enlace</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
+        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>Enlace</v>
+        <v>Creador de pantalla V4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
+        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
+        <v>Pantalla RGB V5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>Creador de pantalla V4</v>
+        <v>suelta un perfil de pantalla</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>Pantalla RGB V5</v>
+        <v>suelta un perfil de observador</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>suelta un perfil de pantalla</v>
+        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Crear perfil de pantalla V4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>suelta un perfil de observador</v>
+        <v>Nombre del perfil</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
+        <v>Crear</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>Crear perfil de pantalla V4</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>Nombre del perfil</v>
+        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>Crear</v>
+        <v>Flujo de enlace</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>Creando…</v>
+        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
+        <v>Hecho</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>Flujo de enlace</v>
+        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
+        <v>Comprobando imagen…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>Hecho</v>
+        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
+        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>Comprobando imagen…</v>
+        <v>Transformar imagen</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
+        <v>Suelta perfiles para iniciar la cadena</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>Transformar imagen</v>
+        <v>eliminado</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>Transformando…</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>Suelta perfiles para iniciar la cadena</v>
+        <v>Mover después</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>eliminado</v>
+        <v>Subir</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>Mover antes</v>
+        <v>Bajar</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>Mover después</v>
+        <v>Intención de renderizado (todas)</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>Subir</v>
+        <v>Intención de renderizado para esta transformación</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>Bajar</v>
+        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>Intención de renderizado (todas)</v>
+        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>Intención de renderizado para esta transformación</v>
+        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
+        <v>Cadena</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
+        <v>No se pudo analizar la cadena.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
+        <v>Comprobando cadena…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>Cadena</v>
+        <v>La cadena no conecta ({detail}).</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>No se pudo analizar la cadena.</v>
+        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>Comprobando cadena…</v>
+        <v>Corrige la cadena antes de procesar imágenes</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>La cadena no conecta ({detail}).</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>Corrige la cadena antes de procesar imágenes</v>
+        <v>Nombre del DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>Borrar</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>Nombre del DeviceLink</v>
+        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>Creando…</v>
+        <v>Crea una cadena para procesar imágenes</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
+        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
+        <v>Imagen transformada guardada.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>Crea una cadena para procesar imágenes</v>
+        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>Imagen transformada guardada.</v>
+        <v>Archivo de datos demasiado grande.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformar datos</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>Archivo de datos demasiado grande.</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>Transformar datos</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>Transformando…</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>Preferir</v>
+        <v>Condición</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>Observador</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>Iluminante</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>Condición</v>
+        <v>media</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>parches</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>mediana</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>media</v>
+        <v>Resultado de la transformación</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>parches</v>
+        <v>{src} → {dst} · {n} parches</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>{n} duplicados</v>
+        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>Resultado de la transformación</v>
+        <v>Guardar como</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · {n} parches</v>
+        <v>Guardar</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
+        <v>Invertir transformación</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>Guardar como</v>
+        <v>Invirtiendo…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>Guardar</v>
+        <v>Invertir</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>Invertir transformación</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>Invirtiendo…</v>
+        <v>primera etapa</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>Invertir</v>
+        <v>Datos en {in} → buscar {out}</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>última etapa</v>
+        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>primera etapa</v>
+        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>Datos en {in} → buscar {out}</v>
+        <v>Coste ΔE</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
+        <v>Esta imagen tiene un perfil ICC incrustado.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
+        <v>Extraer y añadir a la cadena</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>Coste ΔE</v>
+        <v>Extrayendo…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>Esta imagen tiene un perfil ICC incrustado.</v>
+        <v>Descartar</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>Extraer y añadir a la cadena</v>
+        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>Extrayendo…</v>
+        <v>Opciones de salida de imagen</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>Descartar</v>
+        <v>Codificación</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
+        <v>Igual que el origen</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>Opciones de salida de imagen</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>Codificación</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>Igual que el origen</v>
+        <v>Flotante (32 bits)</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8 bits</v>
+        <v>Compresión</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16 bits</v>
+        <v>Ninguna</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>Flotante (32 bits)</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>Compresión</v>
+        <v>Compuesto</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>Ninguna</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>Planar</v>
+        <v>Interpolación CMM</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>Compuesto</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>Separado</v>
+        <v>Lineal</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>Interpolación CMM</v>
+        <v>Incrustar ICC</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>Tetraédrica</v>
+        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>Lineal</v>
+        <v>Ensamblar TIFF espectral</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>Incrustar ICC</v>
+        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
+        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>Ensamblar TIFF espectral</v>
+        <v>can</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
+        <v>Ensamblar y guardar</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
+        <v>Ensamblando…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>can</v>
+        <v>Se ensamblaron {n} canales.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>Ensamblar y guardar</v>
+        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>Ensamblando…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>Se ensamblaron {n} canales.</v>
+        <v>{n} archivo(s) no cargados</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
+        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>Cancelar</v>
+        <v>Aceptar</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n} archivo(s) no cargados</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
+        <v>o</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>Aceptar</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>o</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>Elegir archivo</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>Encabezado</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>Etiquetas</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>Validación</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>Análisis</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>Propósito de representación</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% tinta</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>Perceptual</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>Saturación</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>Propósito de representación</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>media</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>ΔE de ciclo</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>media</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>máx.</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>Analizando…</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>Análisis</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>Gráfico</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>Salida bruta</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>Curvas</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>Curvas de entrada</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>Curvas de salida</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>Imagen CLUT</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>Imagen de gama</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>Cromaticidad</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>Tabla de la curva</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>Tablas</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>Datos</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>Evaluar</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>Cargando…</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>Entrada</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>Salida</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>Coma flotante</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>Normalizado</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>Legible</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>Cargando…</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>Seguridad</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>Conformidad</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>Calidad</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>INFORME</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>FALLIDO</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>comprobaciones</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>Suscribirse</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>Cerrar</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>Correo electrónico</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>(opcional)</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>Cancelar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>Suscribirse</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>Cerrar</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>Error:</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>Convertir a XML</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>ID del perfil</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>Desplazamiento</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>Tamaño</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>Relleno</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>Tipo</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>Array de {type}</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>(Sin contenido)</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>bytes</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>Sin salida de validación</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>El perfil es válido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>Error de validación crítico</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>Válido</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>Advertencia</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>Error</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>Desconocido</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>Aprobado</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>Fallido</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>Ver en contexto</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>Detalle de validación</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>Activado por</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>Campo</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>Valor actual</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>Requerido: 0</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>Esperado: {value}</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>No válido</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>Cerrar</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>ordenar claves</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>sangría</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>ordenar claves</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,3285 +413,3293 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>Ida y vuelta (PRMG)</v>
+        <v>El {pct} % de las muestras estaba fuera de rango y se recortó.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>Ida y vuelta sobre el cubo del dispositivo del perfil, igual que la herramienta de referencia iccRoundTrip. La ida y vuelta 1 es el error dispositivo→PCS→dispositivo (ΔE*ab); la ida y vuelta 2 mide la estabilidad del ciclo PCS. El histograma PRMG indica la interoperabilidad respecto al Perceptual Reference Medium Gamut.</v>
+        <v>Ida y vuelta (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>Usar etiquetas MPE (color)</v>
+        <v>Ida y vuelta sobre el cubo del dispositivo del perfil, igual que la herramienta de referencia iccRoundTrip. La ida y vuelta 1 es el error dispositivo→PCS→dispositivo (ΔE*ab); la ida y vuelta 2 mide la estabilidad del ciclo PCS. El histograma PRMG indica la interoperabilidad respecto al Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>Este perfil no admite ida y vuelta: carece de las transformaciones dispositivo↔PCS necesarias (p. ej. un perfil unidireccional o abstracto).</v>
+        <v>Usar etiquetas MPE (color)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>Ida y vuelta omitida: el espacio de color del dispositivo es demasiado amplio para evaluar (demasiadas muestras).</v>
+        <v>Este perfil no admite ida y vuelta: carece de las transformaciones dispositivo↔PCS necesarias (p. ej. un perfil unidireccional o abstracto).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>Métrica</v>
+        <v>Ida y vuelta omitida: el espacio de color del dispositivo es demasiado amplio para evaluar (demasiadas muestras).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>Ida y vuelta 1</v>
+        <v>Métrica</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>Ida y vuelta 2</v>
+        <v>Ida y vuelta 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>dispositivo → PCS → dispositivo</v>
+        <v>Ida y vuelta 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>estabilidad del ciclo PCS</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>ΔE mín</v>
+        <v>estabilidad del ciclo PCS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>ΔE medio</v>
+        <v>ΔE mín</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>ΔE máx</v>
+        <v>ΔE medio</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>Peor L, a, b</v>
+        <v>ΔE máx</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>Gama especificada</v>
+        <v>Peor L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Gama especificada</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>No especificada</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>No evaluada</v>
+        <v>No especificada</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>Interoperabilidad PRMG</v>
+        <v>No evaluada</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>ΔE de ida y vuelta</v>
+        <v>Interoperabilidad PRMG</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>Recuento</v>
+        <v>ΔE de ida y vuelta</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>Proporción</v>
+        <v>Recuento</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>Total</v>
+        <v>Proporción</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG no evaluado</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>Métricas de todo el perfil para un propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y una métrica de precisión de ida y vuelta. Elige el propósito de representación y el tipo de ida y vuelta — la tabla y el histograma se actualizan en consecuencia.</v>
+        <v>PRMG no evaluado</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>Tipo de ida y vuelta</v>
+        <v>Métricas de todo el perfil para un propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y una métrica de precisión de ida y vuelta. Elige el propósito de representación y el tipo de ida y vuelta — la tabla y el histograma se actualizan en consecuencia.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>No afecta a este tipo de ida y vuelta</v>
+        <v>Tipo de ida y vuelta</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>Este tipo de ida y vuelta no está disponible para este perfil.</v>
+        <v>No afecta a este tipo de ida y vuelta</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>Distribución del ΔE de ida y vuelta</v>
+        <v>Este tipo de ida y vuelta no está disponible para este perfil.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>Ninguna muestra de ida y vuelta cayó dentro de la región evaluada.</v>
+        <v>Distribución del ΔE de ida y vuelta</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>Desv. típica</v>
+        <v>Ninguna muestra de ida y vuelta cayó dentro de la región evaluada.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>Frecuencia relativa</v>
+        <v>Desv. típica</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Frecuencia acumulada</v>
+        <v>Frecuencia relativa</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>Escala horizontal</v>
+        <v>Frecuencia acumulada</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>ΔE entero</v>
+        <v>Escala horizontal</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>Escala automática</v>
+        <v>ΔE entero</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>Clases</v>
+        <v>Escala automática</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>Imagen CLUT</v>
+        <v>Clases</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>La tabla de consulta de color (CLUT) de una transformación dispositivo↔PCS, dispuesta en mosaico en una imagen. Elige qué tabla de propósito de representación mostrar.</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>Este perfil no tiene tablas dispositivo↔PCS basadas en CLUT para visualizar.</v>
+        <v>La tabla de consulta de color (CLUT) de una transformación dispositivo↔PCS, dispuesta en mosaico en una imagen. Elige qué tabla de propósito de representación mostrar.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>Imagen de gama</v>
+        <v>Este perfil no tiene tablas dispositivo↔PCS basadas en CLUT para visualizar.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>El mapa dentro/fuera de gama de la etiqueta gamut: neutro donde un color PCS es reproducible, rojo donde queda fuera de la gama del dispositivo.</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>Este perfil no tiene etiqueta gamut para visualizar.</v>
+        <v>El mapa dentro/fuera de gama de la etiqueta gamut: neutro donde un color PCS es reproducible, rojo donde queda fuera de la gama del dispositivo.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>Escala vertical</v>
+        <v>Este perfil no tiene etiqueta gamut para visualizar.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>Escala vertical</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>Incremento tonal</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>Incremento tonal (salida − entrada)</v>
+        <v>Incremento tonal</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>Mostrar volcado completo</v>
+        <v>Incremento tonal (salida − entrada)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>Salida truncada por rendimiento.</v>
+        <v>Mostrar volcado completo</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>Resumen dentro de gama (RT0)</v>
+        <v>Salida truncada por rendimiento.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>Inversión + gama (RT1)</v>
+        <v>Resumen dentro de gama (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>Reproducibilidad (RT2)</v>
+        <v>Inversión + gama (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>Interoperabilidad PRMG</v>
+        <v>Reproducibilidad (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>Resumen de iccviz: una cuadrícula de valores de dispositivo se lleva al PCS, de vuelta al dispositivo y de nuevo al PCS; se mide el ΔE*ab entre las dos pasadas de PCS. Una comprobación rápida de estabilidad dentro de la gama.</v>
+        <v>Interoperabilidad PRMG</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip Ida y vuelta 1: ΔE*ab entre el PCS de cada color de dispositivo y su PCS tras una ida y vuelta Lab → dispositivo → Lab. Refleja la precisión de inversión y el mapeo de gama.</v>
+        <v>Resumen de iccviz: una cuadrícula de valores de dispositivo se lleva al PCS, de vuelta al dispositivo y de nuevo al PCS; se mide el ΔE*ab entre las dos pasadas de PCS. Una comprobación rápida de estabilidad dentro de la gama.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Ida y vuelta 2: ΔE*ab entre la primera y la segunda ida y vuelta — cómo de estable es una ida y vuelta de PCS repetida (reproducibilidad, independiente del recorte de gama de la primera pasada).</v>
+        <v>iccRoundTrip Ida y vuelta 1: ΔE*ab entre el PCS de cada color de dispositivo y su PCS tras una ida y vuelta Lab → dispositivo → Lab. Refleja la precisión de inversión y el mapeo de gama.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG: los colores PCS dentro del Perceptual Reference Medium Gamut realizan una única ida y vuelta (Lab → dispositivo → Lab); la distribución del ΔE*ab indica la interoperabilidad entre perfiles.</v>
+        <v>iccRoundTrip Ida y vuelta 2: ΔE*ab entre la primera y la segunda ida y vuelta — cómo de estable es una ida y vuelta de PCS repetida (reproducibilidad, independiente del recorte de gama de la primera pasada).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>Ajustes</v>
+        <v>iccRoundTrip PRMG: los colores PCS dentro del Perceptual Reference Medium Gamut realizan una única ida y vuelta (Lab → dispositivo → Lab); la distribución del ΔE*ab indica la interoperabilidad entre perfiles.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>Visualización</v>
+        <v>Ajustes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>Fondo</v>
+        <v>Visualización</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>Idioma</v>
+        <v>Fondo</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>Sistema</v>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>Claro</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>Oscuro</v>
+        <v>Claro</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>Predeterminado del sistema</v>
+        <v>Oscuro</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>Formato numérico</v>
+        <v>Predeterminado del sistema</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>Hexadecimal</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>Ayuda</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>Contacto</v>
+        <v>Ayuda</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>Guía del usuario</v>
+        <v>Contacto</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>Buscar en la guía</v>
+        <v>Guía del usuario</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>Buscar en la guía del usuario</v>
+        <v>Buscar en la guía</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>Resultado anterior</v>
+        <v>Buscar en la guía del usuario</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>Resultado siguiente</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>Cerrar la guía</v>
+        <v>Resultado siguiente</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Cargando…</v>
+        <v>Cerrar la guía</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>No se pudo cargar la guía del usuario.</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>Ninguno</v>
+        <v>No se pudo cargar la guía del usuario.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Ninguno</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v>Basado en la implementación de demostración de</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>Validando…</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>Perfiles</v>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>Mostrar el conjunto de perfiles</v>
+        <v>Perfiles</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>Contraer</v>
+        <v>Mostrar el conjunto de perfiles</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>Cargar perfiles</v>
+        <v>Contraer</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>Quitar</v>
+        <v>Cargar perfiles</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>Suelta perfiles ICC aquí</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>o una imagen (TIFF/PNG/JPEG) para extraer su perfil incrustado — los archivos permanecen en tu dispositivo.</v>
+        <v>Suelta perfiles ICC aquí</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>Nuevo desde .cube</v>
+        <v>o una imagen (TIFF/PNG/JPEG) para extraer su perfil incrustado — los archivos permanecen en tu dispositivo.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>Ordenar por nombre</v>
+        <v>Nuevo desde .cube</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nombre</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>Nuevo perfil desde .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
+        <v>Nuevo perfil desde .cube</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>Elegir archivo .cube</v>
+        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Elegir archivo .cube</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>o suéltalo aquí, o pega debajo</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>Creando…</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>Perfil</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>Enlazar</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>Espectral</v>
+        <v>Enlazar</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>Arrastra perfiles del conjunto a esta pestaña</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>Quitar</v>
+        <v>Arrastra perfiles del conjunto a esta pestaña</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>Ningún perfil seleccionado</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
+        <v>Ningún perfil seleccionado</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>Aún no hay nada que comparar</v>
+        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
+        <v>Aún no hay nada que comparar</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>Comparación de gama</v>
+        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
+        <v>Comparación de gama</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>Propósito de representación</v>
+        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>Envoltura</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>Malla</v>
+        <v>Envoltura</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>Números de eje</v>
+        <v>Malla</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>Opacidad</v>
+        <v>Números de eje</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Color</v>
+        <v>Opacidad</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Sólido</v>
+        <v>Color</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Por tono</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Rotación</v>
+        <v>Por tono</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Plataforma giratoria</v>
+        <v>Rotación</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Órbita</v>
+        <v>Plataforma giratoria</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Velocidad de arrastre</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Alabeo</v>
+        <v>Velocidad de arrastre</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Velocidad de alabeo</v>
+        <v>Alabeo</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Construyendo la gama…</v>
+        <v>Velocidad de alabeo</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>sin gama</v>
+        <v>Construyendo la gama…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sin gama</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Envoltura de gama 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Corte de gama 2D</v>
+        <v>Envoltura de gama 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Plano</v>
+        <v>Corte de gama 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Enlace</v>
+        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
+        <v>Enlace</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
+        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Creador de pantalla V4</v>
+        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
+        <v>Creador de pantalla V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>Pantalla RGB V5</v>
+        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>suelta un perfil de pantalla</v>
+        <v>Pantalla RGB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>suelta un perfil de pantalla</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>suelta un perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
+        <v>suelta un perfil de observador</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Crear perfil de pantalla V4</v>
+        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Nombre del perfil</v>
+        <v>Crear perfil de pantalla V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Crear</v>
+        <v>Nombre del perfil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Creando…</v>
+        <v>Crear</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Flujo de enlace</v>
+        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
+        <v>Flujo de enlace</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>Hecho</v>
+        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
+        <v>Hecho</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>Comprobando imagen…</v>
+        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
+        <v>Comprobando imagen…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
+        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>Transformar imagen</v>
+        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>Transformando…</v>
+        <v>Transformar imagen</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>Suelta perfiles para iniciar la cadena</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>eliminado</v>
+        <v>Suelta perfiles para iniciar la cadena</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>Mover antes</v>
+        <v>eliminado</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>Mover después</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>Subir</v>
+        <v>Mover después</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>Bajar</v>
+        <v>Subir</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>Intención de renderizado (todas)</v>
+        <v>Bajar</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>Intención de renderizado para esta transformación</v>
+        <v>Intención de renderizado (todas)</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
+        <v>Intención de renderizado para esta transformación</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
+        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
+        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>Cadena</v>
+        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>No se pudo analizar la cadena.</v>
+        <v>Cadena</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>Comprobando cadena…</v>
+        <v>No se pudo analizar la cadena.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>La cadena no conecta ({detail}).</v>
+        <v>Comprobando cadena…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
+        <v>La cadena no conecta ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>Corrige la cadena antes de procesar imágenes</v>
+        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>Borrar</v>
+        <v>Corrige la cadena antes de procesar imágenes</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>Nombre del DeviceLink</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>Creando…</v>
+        <v>Nombre del DeviceLink</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
+        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>Crea una cadena para procesar imágenes</v>
+        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
+        <v>Crea una cadena para procesar imágenes</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>Imagen transformada guardada.</v>
+        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagen transformada guardada.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>Archivo de datos demasiado grande.</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>Transformar datos</v>
+        <v>Archivo de datos demasiado grande.</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformando…</v>
+        <v>Transformar datos</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>Preferir</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>Condición</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condición</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>media</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>parches</v>
+        <v>media</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>{n} duplicados</v>
+        <v>parches</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>Resultado de la transformación</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · {n} parches</v>
+        <v>Resultado de la transformación</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
+        <v>{src} → {dst} · {n} parches</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>Guardar como</v>
+        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>Guardar</v>
+        <v>Guardar como</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>Invertir transformación</v>
+        <v>Guardar</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>Invirtiendo…</v>
+        <v>Invertir transformación</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>Invertir</v>
+        <v>Invirtiendo…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>última etapa</v>
+        <v>Invertir</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>primera etapa</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>Datos en {in} → buscar {out}</v>
+        <v>primera etapa</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
+        <v>Datos en {in} → buscar {out}</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
+        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>Coste ΔE</v>
+        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>Esta imagen tiene un perfil ICC incrustado.</v>
+        <v>Coste ΔE</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Extraer y añadir a la cadena</v>
+        <v>Esta imagen tiene un perfil ICC incrustado.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extrayendo…</v>
+        <v>Extraer y añadir a la cadena</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>Descartar</v>
+        <v>Extrayendo…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
+        <v>Descartar</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>Opciones de salida de imagen</v>
+        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>Codificación</v>
+        <v>Opciones de salida de imagen</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>Igual que el origen</v>
+        <v>Codificación</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8 bits</v>
+        <v>Igual que el origen</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>Flotante (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>Compresión</v>
+        <v>Flotante (32 bits)</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>Ninguna</v>
+        <v>Compresión</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>Planar</v>
+        <v>Ninguna</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>Compuesto</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>Separado</v>
+        <v>Compuesto</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>Interpolación CMM</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolación CMM</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>Lineal</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>Incrustar ICC</v>
+        <v>Lineal</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
+        <v>Incrustar ICC</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>Ensamblar TIFF espectral</v>
+        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
+        <v>Ensamblar TIFF espectral</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
+        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>can</v>
+        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>Ensamblar y guardar</v>
+        <v>can</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>Ensamblando…</v>
+        <v>Ensamblar y guardar</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>Se ensamblaron {n} canales.</v>
+        <v>Ensamblando…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
+        <v>Se ensamblaron {n} canales.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>Cancelar</v>
+        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} archivo(s) no cargados</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
+        <v>{n} archivo(s) no cargados</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>Aceptar</v>
+        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Aceptar</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>o</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>Elegir archivo</v>
+        <v>o</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>Encabezado</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>Etiquetas</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>Validación</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>Análisis</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>Propósito de representación</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% tinta</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>Perceptual</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>Saturación</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>Propósito de representación</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>ΔE de ciclo</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>media</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>Analizando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>Análisis</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>Gráfico</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>Salida bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>Curvas de salida</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Imagen CLUT</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>Imagen de gama</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>Cromaticidad</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>Tabla de la curva</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>Tablas</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>Datos</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>Evaluar</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>Cargando…</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>Entrada</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>Salida</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>Coma flotante</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>Normalizado</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>Legible</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>Cargando…</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>Seguridad</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>Conformidad</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>Calidad</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>INFORME</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>Correo electrónico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>(opcional)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>Cancelar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>Suscribirse</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>Cerrar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>Error:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2555,1151 +2555,1423 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>Perceptual</v>
+        <v>L* de salida (tono)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>Saturación</v>
+        <v>Colorimetría de los extremos</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Los extremos del rango de reproducción del perfil: el blanco del soporte, el negro más oscuro que imprimirá, la tinta que cuesta ese negro y el punto en el que cada matiz alcanza su máxima saturación.</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>El punto blanco es el color con colorante cero — el soporte desnudo. El punto negro se obtiene pasando el negro del PCS (L*=0, a*=b*=0) por la tabla B2A seleccionada para obtener el entintado que el perfil elige para el negro, y leyendo después ese entintado a través de A2B1. La cobertura total de tinta (TAC) es la suma de ese entintado. La colorimetría absoluta muestra el color propio del soporte; la relativa lo refiere a un blanco perfecto.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>Propósito de representación</v>
+        <v>Punto blanco</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Punto negro</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>ΔE de ciclo</v>
+        <v>Entintado en el punto negro</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>media</v>
+        <v>Este perfil no tiene etiqueta de punto blanco del medio, por lo que la colorimetría absoluta no está disponible.</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>La colorimetría de los extremos solo está disponible para perfiles de salida (impresora) — supone que colorante cero significa soporte desnudo.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>máx.</v>
+        <v>Tinta plena frente a croma máximo</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>Analizando…</v>
+        <v>Dónde queda cada vértice de tinta y el punto más cromático del camino hasta él. Medido a través de A2B1, por lo que estas filas no cambian con el propósito de representación de arriba. En un perfil bien formado ambas filas coinciden; si el croma máximo llega antes de la tinta plena, la tinta añadida más allá de ese punto solo oscurece.</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>Análisis</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>Gráfico</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>Salida bruta</v>
+        <v>Con entintado</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>El croma máximo se alcanza antes de la tinta plena — la tinta más allá de este punto solo oscurece.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>Uso de tinta en las sombras</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>Curvas</v>
+        <v>Cuatro trayectos rectos por el plano a*b* con una claridad constante y deliberadamente oscura, pasados por la tabla B2A seleccionada. Todas las muestras comparten la misma L*, así que cualquier salto brusco o inversión de un colorante procede únicamente del tratamiento del matiz y del croma — la firma de un artefacto de mapeo de gama en las sombras.</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>Curvas de entrada</v>
+        <v>El uso de tinta en las sombras solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>Curvas de salida</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>Imagen CLUT</v>
+        <v>con compensación de punto negro desde</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>Imagen de gama</v>
+        <v>Posición a lo largo del trayecto</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>Cromaticidad</v>
+        <v>Trayecto</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Cian</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>Tabla de la curva</v>
+        <v>Amarillo</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>Tablas</v>
+        <v>Rojo</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>Datos</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>Evaluar</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>Cargando…</v>
+        <v>Negro</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>Entrada</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>Salida</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>Coma flotante</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>Normalizado</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>Legible</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>Cargando…</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>media</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>Seguridad</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>Conformidad</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>Calidad</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>INFORME</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>FALLIDO</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>comprobaciones</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>Suscribirse</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>Cerrar</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>Correo electrónico</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>(opcional)</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>Cancelar</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>Suscribirse</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>Cerrar</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>Error:</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>Convertir a XML</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>Convertir a JSON</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>Convertir a ICC</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>ID del perfil</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>Desplazamiento</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>Tamaño</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>Relleno</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>Tipo</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>Array de {type}</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>(Sin contenido)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>bytes</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>Sin salida de validación</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>El perfil es válido</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>Error de validación crítico</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>Válido</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>Advertencia</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>Error</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>Desconocido</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>Aprobado</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>Fallido</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>Ver en contexto</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>Detalle de validación</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>Activado por</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>Campo</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>Valor actual</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>Requerido: 0</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>Esperado: {value}</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>No válido</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>Cerrar</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>sangría</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>ordenar claves</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Sin salida de validación</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>El perfil es válido</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>El perfil tiene advertencias</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>El perfil no es conforme</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>Error de validación crítico</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>Estado de validación desconocido</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>Crítico — mostrado solo para inspección</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -533,3445 +533,3477 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>Gama especificada</v>
+        <v>ΔE de ida y vuelta por claridad</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (claridad del color solicitado)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>No especificada</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>No evaluada</v>
+        <v>puntos, límite de la gama → neutro</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>Interoperabilidad PRMG</v>
+        <v>Gama especificada</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>ΔE de ida y vuelta</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>Recuento</v>
+        <v>No especificada</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>Proporción</v>
+        <v>No evaluada</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>Total</v>
+        <v>Interoperabilidad PRMG</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG no evaluado</v>
+        <v>ΔE de ida y vuelta</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>Métricas de todo el perfil para un propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y una métrica de precisión de ida y vuelta. Elige el propósito de representación y el tipo de ida y vuelta — la tabla y el histograma se actualizan en consecuencia.</v>
+        <v>Recuento</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>Tipo de ida y vuelta</v>
+        <v>Proporción</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>No afecta a este tipo de ida y vuelta</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>Este tipo de ida y vuelta no está disponible para este perfil.</v>
+        <v>PRMG no evaluado</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>Distribución del ΔE de ida y vuelta</v>
+        <v>Métricas de todo el perfil para un propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y una métrica de precisión de ida y vuelta. Elige el propósito de representación y el tipo de ida y vuelta — la tabla y el histograma se actualizan en consecuencia.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>Ninguna muestra de ida y vuelta cayó dentro de la región evaluada.</v>
+        <v>Tipo de ida y vuelta</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>Desv. típica</v>
+        <v>No afecta a este tipo de ida y vuelta</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>Frecuencia relativa</v>
+        <v>Este tipo de ida y vuelta no está disponible para este perfil.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>Frecuencia acumulada</v>
+        <v>Distribución del ΔE de ida y vuelta</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>Escala horizontal</v>
+        <v>Ninguna muestra de ida y vuelta cayó dentro de la región evaluada.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>ΔE entero</v>
+        <v>Desv. típica</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>Escala automática</v>
+        <v>Frecuencia relativa</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>Clases</v>
+        <v>Frecuencia acumulada</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>Imagen CLUT</v>
+        <v>Escala horizontal</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>La tabla de consulta de color (CLUT) de una transformación dispositivo↔PCS, dispuesta en mosaico en una imagen. Elige qué tabla de propósito de representación mostrar.</v>
+        <v>ΔE entero</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>Este perfil no tiene tablas dispositivo↔PCS basadas en CLUT para visualizar.</v>
+        <v>Escala automática</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>Imagen de gama</v>
+        <v>Clases</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>El mapa dentro/fuera de gama de la etiqueta gamut: neutro donde un color PCS es reproducible, rojo donde queda fuera de la gama del dispositivo.</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>Este perfil no tiene etiqueta gamut para visualizar.</v>
+        <v>La tabla de consulta de color (CLUT) de una transformación dispositivo↔PCS, dispuesta en mosaico en una imagen. Elige qué tabla de propósito de representación mostrar.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>Escala vertical</v>
+        <v>Este perfil no tiene tablas dispositivo↔PCS basadas en CLUT para visualizar.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>Incremento tonal</v>
+        <v>El mapa dentro/fuera de gama de la etiqueta gamut: neutro donde un color PCS es reproducible, rojo donde queda fuera de la gama del dispositivo.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>Incremento tonal (salida − entrada)</v>
+        <v>Este perfil no tiene etiqueta gamut para visualizar.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>Mostrar volcado completo</v>
+        <v>Escala vertical</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>Salida truncada por rendimiento.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>Resumen dentro de gama (RT0)</v>
+        <v>Incremento tonal</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>Inversión + gama (RT1)</v>
+        <v>Incremento tonal (salida − entrada)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>Reproducibilidad (RT2)</v>
+        <v>Mostrar volcado completo</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>Interoperabilidad PRMG</v>
+        <v>Salida truncada por rendimiento.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>Resumen de iccviz: una cuadrícula de valores de dispositivo se lleva al PCS, de vuelta al dispositivo y de nuevo al PCS; se mide el ΔE*ab entre las dos pasadas de PCS. Una comprobación rápida de estabilidad dentro de la gama.</v>
+        <v>Resumen dentro de gama (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Ida y vuelta 1: ΔE*ab entre el PCS de cada color de dispositivo y su PCS tras una ida y vuelta Lab → dispositivo → Lab. Refleja la precisión de inversión y el mapeo de gama.</v>
+        <v>Inversión + gama (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip Ida y vuelta 2: ΔE*ab entre la primera y la segunda ida y vuelta — cómo de estable es una ida y vuelta de PCS repetida (reproducibilidad, independiente del recorte de gama de la primera pasada).</v>
+        <v>Reproducibilidad (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG: los colores PCS dentro del Perceptual Reference Medium Gamut realizan una única ida y vuelta (Lab → dispositivo → Lab); la distribución del ΔE*ab indica la interoperabilidad entre perfiles.</v>
+        <v>Interoperabilidad PRMG</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>Ajustes</v>
+        <v>Resumen de iccviz: una cuadrícula de valores de dispositivo se lleva al PCS, de vuelta al dispositivo y de nuevo al PCS; se mide el ΔE*ab entre las dos pasadas de PCS. Una comprobación rápida de estabilidad dentro de la gama.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>Visualización</v>
+        <v>iccRoundTrip Ida y vuelta 1: ΔE*ab entre el PCS de cada color de dispositivo y su PCS tras una ida y vuelta Lab → dispositivo → Lab. Refleja la precisión de inversión y el mapeo de gama.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>Fondo</v>
+        <v>iccRoundTrip Ida y vuelta 2: ΔE*ab entre la primera y la segunda ida y vuelta — cómo de estable es una ida y vuelta de PCS repetida (reproducibilidad, independiente del recorte de gama de la primera pasada).</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>Idioma</v>
+        <v>iccRoundTrip PRMG: los colores PCS dentro del Perceptual Reference Medium Gamut realizan una única ida y vuelta (Lab → dispositivo → Lab); la distribución del ΔE*ab indica la interoperabilidad entre perfiles.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>Sistema</v>
+        <v>Ajustes</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>Claro</v>
+        <v>Visualización</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>Oscuro</v>
+        <v>Fondo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>Predeterminado del sistema</v>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>Formato numérico</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>Hexadecimal</v>
+        <v>Claro</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>Decimal</v>
+        <v>Oscuro</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>Ayuda</v>
+        <v>Predeterminado del sistema</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>Contacto</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>Guía del usuario</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>Buscar en la guía</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>Buscar en la guía del usuario</v>
+        <v>Ayuda</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>Resultado anterior</v>
+        <v>Contacto</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>Resultado siguiente</v>
+        <v>Guía del usuario</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Cerrar la guía</v>
+        <v>Buscar en la guía</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>Cargando…</v>
+        <v>Buscar en la guía del usuario</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>No se pudo cargar la guía del usuario.</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>Ninguno</v>
+        <v>Resultado siguiente</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Cerrar la guía</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v>Basado en la implementación de demostración de</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>No se pudo cargar la guía del usuario.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>Validando…</v>
+        <v>Ninguno</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● Modificado — sin guardar</v>
+        <v>Basado en la implementación de demostración de</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>Perfiles</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>Mostrar el conjunto de perfiles</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>Contraer</v>
+        <v>Guardar perfil ICC</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>Cargar perfiles</v>
+        <v>● Modificado — sin guardar</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>Quitar</v>
+        <v>Perfiles</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>Suelta perfiles ICC aquí</v>
+        <v>Mostrar el conjunto de perfiles</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>o una imagen (TIFF/PNG/JPEG) para extraer su perfil incrustado — los archivos permanecen en tu dispositivo.</v>
+        <v>Contraer</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>Nuevo desde .cube</v>
+        <v>Cargar perfiles</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>Ordenar por nombre</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>Suelta perfiles ICC aquí</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>Nuevo perfil desde .cube</v>
+        <v>o una imagen (TIFF/PNG/JPEG) para extraer su perfil incrustado — los archivos permanecen en tu dispositivo.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
+        <v>Nuevo desde .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>Elegir archivo .cube</v>
+        <v>Ordenar por nombre</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Nuevo perfil desde .cube</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Elegir archivo .cube</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>o suéltalo aquí, o pega debajo</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Crear DeviceLink</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Creando…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>No se pudo leer ese archivo.</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>Perfil</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>Comparar</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>Enlazar</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>Espectral</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>Arrastra perfiles del conjunto a esta pestaña</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>Quitar</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>Ningún perfil seleccionado</v>
+        <v>Enlazar</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>Aún no hay nada que comparar</v>
+        <v>Arrastra perfiles del conjunto a esta pestaña</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>Comparación de gama</v>
+        <v>Ningún perfil seleccionado</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
+        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>Propósito de representación</v>
+        <v>Aún no hay nada que comparar</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>Envoltura</v>
+        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>Malla</v>
+        <v>Comparación de gama</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>Números de eje</v>
+        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacidad</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>Color</v>
+        <v>Envoltura</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>Sólido</v>
+        <v>Malla</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>Por valor</v>
+        <v>Números de eje</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>Por tono</v>
+        <v>Opacidad</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotación</v>
+        <v>Color</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>Plataforma giratoria</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>Órbita</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>Velocidad de arrastre</v>
+        <v>Por tono</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>Alabeo</v>
+        <v>Rotación</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocidad de alabeo</v>
+        <v>Plataforma giratoria</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>Construyendo la gama…</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>sin gama</v>
+        <v>Velocidad de arrastre</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Alabeo</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>Envoltura de gama 3D</v>
+        <v>Velocidad de alabeo</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>Corte de gama 2D</v>
+        <v>Construyendo la gama…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>Plano</v>
+        <v>sin gama</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Envoltura de gama 3D</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>Corte de gama 2D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>Enlace</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>Creador de pantalla V4</v>
+        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
+        <v>Enlace</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>Pantalla RGB V5</v>
+        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>suelta un perfil de pantalla</v>
+        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Creador de pantalla V4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>suelta un perfil de observador</v>
+        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
+        <v>Pantalla RGB V5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Crear perfil de pantalla V4</v>
+        <v>suelta un perfil de pantalla</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>Nombre del perfil</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Crear</v>
+        <v>suelta un perfil de observador</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>Creando…</v>
+        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
+        <v>Crear perfil de pantalla V4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>Flujo de enlace</v>
+        <v>Nombre del perfil</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
+        <v>Crear</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>Hecho</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
+        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>Comprobando imagen…</v>
+        <v>Flujo de enlace</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
+        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
+        <v>Hecho</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>Transformar imagen</v>
+        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>Transformando…</v>
+        <v>Comprobando imagen…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>Suelta perfiles para iniciar la cadena</v>
+        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>eliminado</v>
+        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>Mover antes</v>
+        <v>Transformar imagen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>Mover después</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>Subir</v>
+        <v>Suelta perfiles para iniciar la cadena</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>Bajar</v>
+        <v>eliminado</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>Intención de renderizado (todas)</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>Intención de renderizado para esta transformación</v>
+        <v>Mover después</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
+        <v>Subir</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
+        <v>Bajar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
+        <v>Intención de renderizado (todas)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>Cadena</v>
+        <v>Intención de renderizado para esta transformación</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>No se pudo analizar la cadena.</v>
+        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>Comprobando cadena…</v>
+        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>La cadena no conecta ({detail}).</v>
+        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
+        <v>Cadena</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>Corrige la cadena antes de procesar imágenes</v>
+        <v>No se pudo analizar la cadena.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>Borrar</v>
+        <v>Comprobando cadena…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>Crear DeviceLink</v>
+        <v>La cadena no conecta ({detail}).</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Nombre del DeviceLink</v>
+        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>Creando…</v>
+        <v>Corrige la cadena antes de procesar imágenes</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>Crea una cadena para procesar imágenes</v>
+        <v>Nombre del DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>Imagen transformada guardada.</v>
+        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
+        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Crea una cadena para procesar imágenes</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>Archivo de datos demasiado grande.</v>
+        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformar datos</v>
+        <v>Imagen transformada guardada.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>Transformando…</v>
+        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>Preferir</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>Observador</v>
+        <v>Archivo de datos demasiado grande.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>Iluminante</v>
+        <v>Transformar datos</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>Condición</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>mediana</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>media</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>parches</v>
+        <v>Condición</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} duplicados</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>Resultado de la transformación</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · {n} parches</v>
+        <v>media</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
+        <v>parches</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>Guardar como</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>Guardar</v>
+        <v>Resultado de la transformación</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>Invertir transformación</v>
+        <v>{src} → {dst} · {n} parches</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>Invirtiendo…</v>
+        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>Invertir</v>
+        <v>Guardar como</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>última etapa</v>
+        <v>Guardar</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>primera etapa</v>
+        <v>Invertir transformación</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>Datos en {in} → buscar {out}</v>
+        <v>Invirtiendo…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
+        <v>Invertir</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>Coste ΔE</v>
+        <v>primera etapa</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>Esta imagen tiene un perfil ICC incrustado.</v>
+        <v>Datos en {in} → buscar {out}</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extraer y añadir a la cadena</v>
+        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>Extrayendo…</v>
+        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>Descartar</v>
+        <v>Coste ΔE</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
+        <v>Esta imagen tiene un perfil ICC incrustado.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>Opciones de salida de imagen</v>
+        <v>Extraer y añadir a la cadena</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>Codificación</v>
+        <v>Extrayendo…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>Igual que el origen</v>
+        <v>Descartar</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8 bits</v>
+        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16 bits</v>
+        <v>Opciones de salida de imagen</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>Flotante (32 bits)</v>
+        <v>Codificación</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>Compresión</v>
+        <v>Igual que el origen</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>Ninguna</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>Planar</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>Compuesto</v>
+        <v>Flotante (32 bits)</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>Separado</v>
+        <v>Compresión</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>Interpolación CMM</v>
+        <v>Ninguna</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>Tetraédrica</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>Lineal</v>
+        <v>Compuesto</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>Incrustar ICC</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
+        <v>Interpolación CMM</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>Ensamblar TIFF espectral</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
+        <v>Lineal</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
+        <v>Incrustar ICC</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>can</v>
+        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>Ensamblar y guardar</v>
+        <v>Ensamblar TIFF espectral</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>Ensamblando…</v>
+        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>Se ensamblaron {n} canales.</v>
+        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
+        <v>can</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>Cancelar</v>
+        <v>Ensamblar y guardar</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n} archivo(s) no cargados</v>
+        <v>Ensamblando…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
+        <v>Se ensamblaron {n} canales.</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>Aceptar</v>
+        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>o</v>
+        <v>{n} archivo(s) no cargados</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>Elegir archivo</v>
+        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Aceptar</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>Encabezado</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>Etiquetas</v>
+        <v>o</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>Validación</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>Análisis</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>Propósito de representación</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% tinta</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* de salida (tono)</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimetría de los extremos</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>Los extremos del rango de reproducción del perfil: el blanco del soporte, el negro más oscuro que imprimirá, la tinta que cuesta ese negro y el punto en el que cada matiz alcanza su máxima saturación.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>El punto blanco es el color con colorante cero — el soporte desnudo. El punto negro se obtiene pasando el negro del PCS (L*=0, a*=b*=0) por la tabla B2A seleccionada para obtener el entintado que el perfil elige para el negro, y leyendo después ese entintado a través de A2B1. La cobertura total de tinta (TAC) es la suma de ese entintado. La colorimetría absoluta muestra el color propio del soporte; la relativa lo refiere a un blanco perfecto.</v>
+        <v>L* de salida (tono)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>Relativa</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>Absoluta</v>
+        <v>Colorimetría de los extremos</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>Punto blanco</v>
+        <v>Los extremos del rango de reproducción del perfil: el blanco del soporte, el negro más oscuro que imprimirá, la tinta que cuesta ese negro y el punto en el que cada matiz alcanza su máxima saturación.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>Punto negro</v>
+        <v>El punto blanco es el color con colorante cero — el soporte desnudo. El punto negro se obtiene pasando el negro del PCS (L*=0, a*=b*=0) por la tabla B2A seleccionada para obtener el entintado que el perfil elige para el negro, y leyendo después ese entintado a través de A2B1. La cobertura total de tinta (TAC) es la suma de ese entintado. La colorimetría absoluta muestra el color propio del soporte; la relativa lo refiere a un blanco perfecto.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>Entintado en el punto negro</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>Este perfil no tiene etiqueta de punto blanco del medio, por lo que la colorimetría absoluta no está disponible.</v>
+        <v>Punto blanco</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>La colorimetría de los extremos solo está disponible para perfiles de salida (impresora) — supone que colorante cero significa soporte desnudo.</v>
+        <v>Punto negro</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Tinta plena frente a croma máximo</v>
+        <v>Entintado en el punto negro</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>Dónde queda cada vértice de tinta y el punto más cromático del camino hasta él. Medido a través de A2B1, por lo que estas filas no cambian con el propósito de representación de arriba. En un perfil bien formado ambas filas coinciden; si el croma máximo llega antes de la tinta plena, la tinta añadida más allá de ese punto solo oscurece.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>Matiz</v>
+        <v>Este perfil no tiene etiqueta de punto blanco del medio, por lo que la colorimetría absoluta no está disponible.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>Tinta plena</v>
+        <v>La colorimetría de los extremos solo está disponible para perfiles de salida (impresora) — supone que colorante cero significa soporte desnudo.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena frente a croma máximo</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>Con entintado</v>
+        <v>Dónde queda cada vértice de tinta y el punto más cromático del camino hasta él. Medido a través de A2B1, por lo que estas filas no cambian con el propósito de representación de arriba. En un perfil bien formado ambas filas coinciden; si el croma máximo llega antes de la tinta plena, la tinta añadida más allá de ese punto solo oscurece.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>El croma máximo se alcanza antes de la tinta plena — la tinta más allá de este punto solo oscurece.</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>Uso de tinta en las sombras</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>Cuatro trayectos rectos por el plano a*b* con una claridad constante y deliberadamente oscura, pasados por la tabla B2A seleccionada. Todas las muestras comparten la misma L*, así que cualquier salto brusco o inversión de un colorante procede únicamente del tratamiento del matiz y del croma — la firma de un artefacto de mapeo de gama en las sombras.</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>El uso de tinta en las sombras solo está disponible para perfiles de salida (impresora).</v>
+        <v>Con entintado</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>Plano de L* constante</v>
+        <v>El croma máximo se alcanza antes de la tinta plena — la tinta más allá de este punto solo oscurece.</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>con compensación de punto negro desde</v>
+        <v>Uso de tinta en las sombras</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>Posición a lo largo del trayecto</v>
+        <v>Cuatro trayectos rectos por el plano a*b* con una claridad constante y deliberadamente oscura, pasados por la tabla B2A seleccionada. Todas las muestras comparten la misma L*, así que cualquier salto brusco o inversión de un colorante procede únicamente del tratamiento del matiz y del croma — la firma de un artefacto de mapeo de gama en las sombras.</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>Trayecto</v>
+        <v>El uso de tinta en las sombras solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>Cian</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>Magenta</v>
+        <v>con compensación de punto negro desde</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>Amarillo</v>
+        <v>Posición a lo largo del trayecto</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>Rojo</v>
+        <v>Trayecto</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>Verde</v>
+        <v>Cian</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>Azul</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>Negro</v>
+        <v>Amarillo</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>Perceptual</v>
+        <v>Rojo</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>Saturación</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Negro</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>Propósito de representación</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>ΔE de ciclo</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>media</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>máx.</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>Analizando…</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>Análisis</v>
+        <v>media</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>Gráfico</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>Salida bruta</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>Curvas</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>Curvas de entrada</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>Curvas de salida</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>Imagen CLUT</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>Imagen de gama</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>Cromaticidad</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>Tabla de la curva</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>Tablas</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>Datos</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>Evaluar</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>Cargando…</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>Entrada</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>Salida</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>Coma flotante</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>Normalizado</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Legible</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>Cargando…</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>Seguridad</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>Conformidad</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>Calidad</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>INFORME</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>FALLIDO</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>comprobaciones</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>Suscribirse</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>Cerrar</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>Correo electrónico</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>(opcional)</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>Cancelar</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>Suscribirse</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>Cerrar</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>Error:</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>Convertir a XML</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>Convertir a JSON</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>Convertir a ICC</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>ID del perfil</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>Desplazamiento</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>Tamaño</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>Relleno</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>Tipo</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>Array de {type}</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>(Sin contenido)</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>bytes</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>Sin salida de validación</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>El perfil es válido</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>Error de validación crítico</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>Válido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>Advertencia</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>Error</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>Desconocido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>Aprobado</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>Fallido</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>Ver en contexto</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>Detalle de validación</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>Activado por</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>Campo</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>Valor actual</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>Requerido: 0</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>Esperado: {value}</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>No válido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>Cerrar</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>sangría</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>ordenar claves</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2803,1207 +2803,1343 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>Cian</v>
+        <v>Trayectorias de entintado primario por el neutro</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>Magenta</v>
+        <v>Tres trayectorias dentro de la gama — cian→rojo, magenta→verde, amarillo→azul — cada una a través del eje neutro en la claridad media de sus extremos, mediante la tabla B2A seleccionada. Cada muestra está dentro de la gama, así que a diferencia de las trayectorias de sombra, cualquier salto o inversión de un colorante es un defecto de suavidad de la CLUT y no un artefacto de mapeo de gama.</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>Amarillo</v>
+        <v>Las trayectorias de entintado primario solo están disponibles para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>Rojo</v>
+        <v>Posición a lo largo de la trayectoria (neutro en el centro)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>Verde</v>
+        <v>Compensación de punto negro aplicada para este propósito.</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>Azul</v>
+        <v>Estadísticas de uso de tinta</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>Negro</v>
+        <v>Cuánto de cada colorante deposita el perfil, como suma y como proporción del total — la firma de consumo de tinta de la separación.</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>Perceptual</v>
+        <v>Las estadísticas de uso de tinta solo están disponibles para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Eje neutro</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>Saturación</v>
+        <v>Cobertura media</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Proporción de tinta</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>La proporción de tinta es la huella de la construcción del neutro — la fracción de cada colorante en el total de tinta depositada, independiente del número de muestras.</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Puntos dentro de la gama</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>El uso de tinta en todos los colores de la gama necesita el contorno de gama del lado B2A, aún no implementado — pendiente.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>Propósito de representación</v>
+        <v>No hay datos de colorante para resumir.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Seleccione una tabla B2A (PCS→dispositivo) abajo para ver también una imagen en escala de grises de la cobertura de tinta de cada colorante.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>ΔE de ciclo</v>
+        <v>Cobertura de tinta de cada colorante sobre la misma retícula (más oscuro = más tinta).</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>Cian</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>media</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>Amarillo</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>máx.</v>
+        <v>Rojo</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>Analizando…</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>Análisis</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Negro</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>Gráfico</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>Salida bruta</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>Curvas</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>Curvas de entrada</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>Curvas de salida</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>Imagen CLUT</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>Imagen de gama</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>Cromaticidad</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>media</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>Tabla de la curva</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>Tablas</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>Datos</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>Evaluar</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>Cargando…</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>Entrada</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Salida</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>Coma flotante</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>Normalizado</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Legible</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>Cargando…</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>Seguridad</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>Conformidad</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>Calidad</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>INFORME</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>FALLIDO</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>comprobaciones</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>Suscribirse</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>Cerrar</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>Correo electrónico</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>(opcional)</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>Cancelar</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>Suscribirse</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>Cerrar</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>Error:</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>Convertir a XML</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>Convertir a JSON</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>Convertir a ICC</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>ID del perfil</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>Desplazamiento</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>Tamaño</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Relleno</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>Tipo</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>Array de {type}</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>(Sin contenido)</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>bytes</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>Sin salida de validación</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>El perfil es válido</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>Error de validación crítico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>Válido</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>Advertencia</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>Error</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>Desconocido</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>Aprobado</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>Fallido</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>Ver en contexto</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>Detalle de validación</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>Activado por</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>Campo</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>Valor actual</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>Requerido: 0</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>Esperado: {value}</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>No válido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>Cerrar</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>Cargando editor XML…</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>sangría</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>ordenar claves</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
   </ignoredErrors>
 </worksheet>
 </file>